--- a/artfynd/A 51949-2025 artfynd.xlsx
+++ b/artfynd/A 51949-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137327443</v>
       </c>
       <c r="B2" t="n">
-        <v>92109</v>
+        <v>92112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137327462</v>
       </c>
       <c r="B3" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137327490</v>
       </c>
       <c r="B4" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137327491</v>
       </c>
       <c r="B5" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137327424</v>
       </c>
       <c r="B6" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137327502</v>
       </c>
       <c r="B7" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137327423</v>
       </c>
       <c r="B8" t="n">
-        <v>83502</v>
+        <v>83505</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137327477</v>
       </c>
       <c r="B9" t="n">
-        <v>78518</v>
+        <v>78521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137327476</v>
       </c>
       <c r="B10" t="n">
-        <v>83496</v>
+        <v>83499</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137327487</v>
       </c>
       <c r="B11" t="n">
-        <v>89520</v>
+        <v>89523</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137327465</v>
       </c>
       <c r="B12" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137327468</v>
       </c>
       <c r="B13" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137327482</v>
       </c>
       <c r="B14" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137327484</v>
       </c>
       <c r="B15" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>137327431</v>
       </c>
       <c r="B16" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>137327436</v>
       </c>
       <c r="B17" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>137327447</v>
       </c>
       <c r="B18" t="n">
-        <v>83502</v>
+        <v>83505</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>137327486</v>
       </c>
       <c r="B19" t="n">
-        <v>80485</v>
+        <v>80488</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>137327435</v>
       </c>
       <c r="B20" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>137327455</v>
       </c>
       <c r="B21" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>137327440</v>
       </c>
       <c r="B22" t="n">
-        <v>92173</v>
+        <v>92176</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>137327453</v>
       </c>
       <c r="B23" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>137327469</v>
       </c>
       <c r="B24" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>137327433</v>
       </c>
       <c r="B25" t="n">
-        <v>92551</v>
+        <v>92554</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>137327467</v>
       </c>
       <c r="B26" t="n">
-        <v>92173</v>
+        <v>92176</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>137327439</v>
       </c>
       <c r="B27" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>137327496</v>
       </c>
       <c r="B28" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>137327437</v>
       </c>
       <c r="B29" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>137327460</v>
       </c>
       <c r="B30" t="n">
-        <v>78518</v>
+        <v>78521</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 51949-2025 artfynd.xlsx
+++ b/artfynd/A 51949-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137327443</v>
       </c>
       <c r="B2" t="n">
-        <v>92112</v>
+        <v>92114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137327462</v>
       </c>
       <c r="B3" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137327490</v>
       </c>
       <c r="B4" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137327491</v>
       </c>
       <c r="B5" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137327465</v>
       </c>
       <c r="B12" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137327468</v>
       </c>
       <c r="B13" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137327482</v>
       </c>
       <c r="B14" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>137327435</v>
       </c>
       <c r="B20" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>137327455</v>
       </c>
       <c r="B21" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>137327440</v>
       </c>
       <c r="B22" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>137327433</v>
       </c>
       <c r="B25" t="n">
-        <v>92554</v>
+        <v>92556</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>137327467</v>
       </c>
       <c r="B26" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 51949-2025 artfynd.xlsx
+++ b/artfynd/A 51949-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137327443</v>
       </c>
       <c r="B2" t="n">
-        <v>92114</v>
+        <v>92119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137327462</v>
       </c>
       <c r="B3" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137327490</v>
       </c>
       <c r="B4" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137327491</v>
       </c>
       <c r="B5" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137327424</v>
       </c>
       <c r="B6" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137327502</v>
       </c>
       <c r="B7" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137327423</v>
       </c>
       <c r="B8" t="n">
-        <v>83505</v>
+        <v>83510</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137327477</v>
       </c>
       <c r="B9" t="n">
-        <v>78521</v>
+        <v>78526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137327476</v>
       </c>
       <c r="B10" t="n">
-        <v>83499</v>
+        <v>83504</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137327487</v>
       </c>
       <c r="B11" t="n">
-        <v>89523</v>
+        <v>89528</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137327465</v>
       </c>
       <c r="B12" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137327468</v>
       </c>
       <c r="B13" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137327482</v>
       </c>
       <c r="B14" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137327484</v>
       </c>
       <c r="B15" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>137327431</v>
       </c>
       <c r="B16" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>137327436</v>
       </c>
       <c r="B17" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>137327447</v>
       </c>
       <c r="B18" t="n">
-        <v>83505</v>
+        <v>83510</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>137327486</v>
       </c>
       <c r="B19" t="n">
-        <v>80488</v>
+        <v>80493</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>137327435</v>
       </c>
       <c r="B20" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>137327455</v>
       </c>
       <c r="B21" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>137327440</v>
       </c>
       <c r="B22" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>137327453</v>
       </c>
       <c r="B23" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>137327469</v>
       </c>
       <c r="B24" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>137327433</v>
       </c>
       <c r="B25" t="n">
-        <v>92556</v>
+        <v>92561</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>137327467</v>
       </c>
       <c r="B26" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>137327439</v>
       </c>
       <c r="B27" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>137327496</v>
       </c>
       <c r="B28" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>137327437</v>
       </c>
       <c r="B29" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>137327460</v>
       </c>
       <c r="B30" t="n">
-        <v>78521</v>
+        <v>78526</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 51949-2025 artfynd.xlsx
+++ b/artfynd/A 51949-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137327443</v>
       </c>
       <c r="B2" t="n">
-        <v>92119</v>
+        <v>92131</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137327462</v>
       </c>
       <c r="B3" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137327490</v>
       </c>
       <c r="B4" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137327491</v>
       </c>
       <c r="B5" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137327424</v>
       </c>
       <c r="B6" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137327502</v>
       </c>
       <c r="B7" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137327423</v>
       </c>
       <c r="B8" t="n">
-        <v>83510</v>
+        <v>83521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137327477</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>78537</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137327476</v>
       </c>
       <c r="B10" t="n">
-        <v>83504</v>
+        <v>83515</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137327487</v>
       </c>
       <c r="B11" t="n">
-        <v>89528</v>
+        <v>89539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137327465</v>
       </c>
       <c r="B12" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137327468</v>
       </c>
       <c r="B13" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137327482</v>
       </c>
       <c r="B14" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137327484</v>
       </c>
       <c r="B15" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>137327431</v>
       </c>
       <c r="B16" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>137327436</v>
       </c>
       <c r="B17" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>137327447</v>
       </c>
       <c r="B18" t="n">
-        <v>83510</v>
+        <v>83521</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>137327486</v>
       </c>
       <c r="B19" t="n">
-        <v>80493</v>
+        <v>80504</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>137327435</v>
       </c>
       <c r="B20" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>137327455</v>
       </c>
       <c r="B21" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>137327440</v>
       </c>
       <c r="B22" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>137327453</v>
       </c>
       <c r="B23" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>137327433</v>
       </c>
       <c r="B25" t="n">
-        <v>92561</v>
+        <v>92573</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>137327467</v>
       </c>
       <c r="B26" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>137327439</v>
       </c>
       <c r="B27" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>137327496</v>
       </c>
       <c r="B28" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>137327437</v>
       </c>
       <c r="B29" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>137327460</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>78537</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 51949-2025 artfynd.xlsx
+++ b/artfynd/A 51949-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137327443</v>
       </c>
       <c r="B2" t="n">
-        <v>92131</v>
+        <v>92132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137327462</v>
       </c>
       <c r="B3" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137327490</v>
       </c>
       <c r="B4" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137327491</v>
       </c>
       <c r="B5" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137327424</v>
       </c>
       <c r="B6" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137327502</v>
       </c>
       <c r="B7" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137327423</v>
       </c>
       <c r="B8" t="n">
-        <v>83521</v>
+        <v>83522</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137327477</v>
       </c>
       <c r="B9" t="n">
-        <v>78537</v>
+        <v>78538</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137327476</v>
       </c>
       <c r="B10" t="n">
-        <v>83515</v>
+        <v>83516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137327487</v>
       </c>
       <c r="B11" t="n">
-        <v>89539</v>
+        <v>89540</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137327465</v>
       </c>
       <c r="B12" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137327468</v>
       </c>
       <c r="B13" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137327482</v>
       </c>
       <c r="B14" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137327484</v>
       </c>
       <c r="B15" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>137327431</v>
       </c>
       <c r="B16" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>137327436</v>
       </c>
       <c r="B17" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>137327447</v>
       </c>
       <c r="B18" t="n">
-        <v>83521</v>
+        <v>83522</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>137327486</v>
       </c>
       <c r="B19" t="n">
-        <v>80504</v>
+        <v>80505</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>137327435</v>
       </c>
       <c r="B20" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>137327455</v>
       </c>
       <c r="B21" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>137327440</v>
       </c>
       <c r="B22" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>137327453</v>
       </c>
       <c r="B23" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>137327433</v>
       </c>
       <c r="B25" t="n">
-        <v>92573</v>
+        <v>92574</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>137327467</v>
       </c>
       <c r="B26" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>137327439</v>
       </c>
       <c r="B27" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>137327496</v>
       </c>
       <c r="B28" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>137327437</v>
       </c>
       <c r="B29" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>137327460</v>
       </c>
       <c r="B30" t="n">
-        <v>78537</v>
+        <v>78538</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 51949-2025 artfynd.xlsx
+++ b/artfynd/A 51949-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137327443</v>
       </c>
       <c r="B2" t="n">
-        <v>92132</v>
+        <v>92135</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137327462</v>
       </c>
       <c r="B3" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137327490</v>
       </c>
       <c r="B4" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137327491</v>
       </c>
       <c r="B5" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137327424</v>
       </c>
       <c r="B6" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137327502</v>
       </c>
       <c r="B7" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137327423</v>
       </c>
       <c r="B8" t="n">
-        <v>83522</v>
+        <v>83524</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137327477</v>
       </c>
       <c r="B9" t="n">
-        <v>78538</v>
+        <v>78540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137327476</v>
       </c>
       <c r="B10" t="n">
-        <v>83516</v>
+        <v>83518</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137327487</v>
       </c>
       <c r="B11" t="n">
-        <v>89540</v>
+        <v>89543</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137327465</v>
       </c>
       <c r="B12" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137327468</v>
       </c>
       <c r="B13" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137327482</v>
       </c>
       <c r="B14" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137327484</v>
       </c>
       <c r="B15" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>137327431</v>
       </c>
       <c r="B16" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>137327436</v>
       </c>
       <c r="B17" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>137327447</v>
       </c>
       <c r="B18" t="n">
-        <v>83522</v>
+        <v>83524</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>137327486</v>
       </c>
       <c r="B19" t="n">
-        <v>80505</v>
+        <v>80507</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>137327435</v>
       </c>
       <c r="B20" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>137327455</v>
       </c>
       <c r="B21" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>137327440</v>
       </c>
       <c r="B22" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>137327453</v>
       </c>
       <c r="B23" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>137327433</v>
       </c>
       <c r="B25" t="n">
-        <v>92574</v>
+        <v>92577</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>137327467</v>
       </c>
       <c r="B26" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>137327439</v>
       </c>
       <c r="B27" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>137327496</v>
       </c>
       <c r="B28" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>137327437</v>
       </c>
       <c r="B29" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>137327460</v>
       </c>
       <c r="B30" t="n">
-        <v>78538</v>
+        <v>78540</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 51949-2025 artfynd.xlsx
+++ b/artfynd/A 51949-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137327443</v>
       </c>
       <c r="B2" t="n">
-        <v>92135</v>
+        <v>92139</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137327462</v>
       </c>
       <c r="B3" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137327490</v>
       </c>
       <c r="B4" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137327491</v>
       </c>
       <c r="B5" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137327424</v>
       </c>
       <c r="B6" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137327502</v>
       </c>
       <c r="B7" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137327423</v>
       </c>
       <c r="B8" t="n">
-        <v>83524</v>
+        <v>83528</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137327477</v>
       </c>
       <c r="B9" t="n">
-        <v>78540</v>
+        <v>78544</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137327476</v>
       </c>
       <c r="B10" t="n">
-        <v>83518</v>
+        <v>83522</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137327487</v>
       </c>
       <c r="B11" t="n">
-        <v>89543</v>
+        <v>89547</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137327465</v>
       </c>
       <c r="B12" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137327468</v>
       </c>
       <c r="B13" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137327482</v>
       </c>
       <c r="B14" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137327484</v>
       </c>
       <c r="B15" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>137327431</v>
       </c>
       <c r="B16" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>137327436</v>
       </c>
       <c r="B17" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>137327447</v>
       </c>
       <c r="B18" t="n">
-        <v>83524</v>
+        <v>83528</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>137327486</v>
       </c>
       <c r="B19" t="n">
-        <v>80507</v>
+        <v>80511</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>137327435</v>
       </c>
       <c r="B20" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>137327455</v>
       </c>
       <c r="B21" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>137327440</v>
       </c>
       <c r="B22" t="n">
-        <v>92199</v>
+        <v>92203</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>137327453</v>
       </c>
       <c r="B23" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>137327469</v>
       </c>
       <c r="B24" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>137327433</v>
       </c>
       <c r="B25" t="n">
-        <v>92577</v>
+        <v>92581</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>137327467</v>
       </c>
       <c r="B26" t="n">
-        <v>92199</v>
+        <v>92203</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>137327439</v>
       </c>
       <c r="B27" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>137327496</v>
       </c>
       <c r="B28" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>137327437</v>
       </c>
       <c r="B29" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>137327460</v>
       </c>
       <c r="B30" t="n">
-        <v>78540</v>
+        <v>78544</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
